--- a/dist/master_template.xlsx
+++ b/dist/master_template.xlsx
@@ -1,41 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carcheme\PycharmProjects\request_template\dist\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473DA213-A1D4-44A4-B8A4-35F71BCA9599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="digestion_page" sheetId="1" r:id="rId1"/>
     <sheet name="200126511" sheetId="2" r:id="rId2"/>
-    <sheet name="formula_page" sheetId="3" r:id="rId3"/>
+    <sheet name="200126512" sheetId="3" r:id="rId3"/>
+    <sheet name="formula_page" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
   <si>
     <t>Date:</t>
   </si>
@@ -52,7 +34,7 @@
     <t>Element(s)</t>
   </si>
   <si>
-    <t>Ag</t>
+    <t>cr6+_EPA</t>
   </si>
   <si>
     <t>SOP#</t>
@@ -76,7 +58,16 @@
     <t>200126511_2</t>
   </si>
   <si>
-    <t>Ag ICP analysis</t>
+    <t>200126512_1</t>
+  </si>
+  <si>
+    <t>200126512_2</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>cr6+_EPA UV-Vis analysis</t>
   </si>
   <si>
     <t>sample</t>
@@ -88,22 +79,43 @@
     <t>conc. [mg/L]</t>
   </si>
   <si>
-    <t>Ag_ppm</t>
-  </si>
-  <si>
-    <t>%Ag</t>
-  </si>
-  <si>
-    <t>ag result:</t>
-  </si>
-  <si>
-    <t>ag oxide factor:</t>
-  </si>
-  <si>
-    <t>ag oxide result:</t>
-  </si>
-  <si>
-    <t>ag lot:</t>
+    <t>cr6+_EPA_ppm</t>
+  </si>
+  <si>
+    <t>%cr6+_EPA</t>
+  </si>
+  <si>
+    <t>cr6+_epa result:</t>
+  </si>
+  <si>
+    <t>cr6+_epa oxide factor:</t>
+  </si>
+  <si>
+    <t>cr6+_epa oxide result:</t>
+  </si>
+  <si>
+    <t>cr6+_epa lot:</t>
+  </si>
+  <si>
+    <t>Cl IC analysis</t>
+  </si>
+  <si>
+    <t>Cl_ppm</t>
+  </si>
+  <si>
+    <t>%Cl</t>
+  </si>
+  <si>
+    <t>cl result:</t>
+  </si>
+  <si>
+    <t>cl oxide factor:</t>
+  </si>
+  <si>
+    <t>cl oxide result:</t>
+  </si>
+  <si>
+    <t>cl lot:</t>
   </si>
   <si>
     <t>Note(s):</t>
@@ -146,26 +158,21 @@
   </si>
   <si>
     <t>%Cr(III) = total_Cr - Cr(VI)</t>
-  </si>
-  <si>
-    <t>lot</t>
-  </si>
-  <si>
-    <t>Blah</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot; ppm&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot; %&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot; ppm&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,12 +248,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -254,32 +264,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -294,21 +294,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -346,7 +338,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -380,7 +372,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -415,10 +406,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -591,24 +581,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -616,101 +606,180 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="15"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="C10" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5">
-        <v>0.10009999999999999</v>
-      </c>
-      <c r="C11" s="4">
-        <v>200</v>
-      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -718,181 +787,313 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="16"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <f>"10/2"</f>
-        <v>10/2</v>
-      </c>
-      <c r="C7" s="7">
-        <v>2.2777777700000001</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="B7" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
         <f>((C7)*(H7)*(I7))/(G7*1)</f>
-        <v>22777.777699999999</v>
-      </c>
-      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
         <f>D7/10000</f>
-        <v>2.2777777699999997</v>
-      </c>
-      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
         <f>digestion_page!B10</f>
-        <v>0.1</v>
-      </c>
-      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
         <f>digestion_page!C10</f>
-        <v>200</v>
-      </c>
-      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
         <f>(LEFT(B7,FIND("/",B7)-1)/RIGHT(B7,LEN(B7)-FIND("/", B7)))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <f>"10/2"</f>
-        <v>10/2</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2.3029999999999999</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="B8" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
         <f>((C8)*(H8)*(I8))/(G8*1)</f>
-        <v>23006.993006993009</v>
-      </c>
-      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
         <f>D8/10000</f>
-        <v>2.3006993006993008</v>
-      </c>
-      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
         <f>digestion_page!B11</f>
-        <v>0.10009999999999999</v>
-      </c>
-      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
         <f>digestion_page!C11</f>
-        <v>200</v>
-      </c>
-      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
         <f>(LEFT(B8,FIND("/",B8)-1)/RIGHT(B8,LEN(B8)-FIND("/", B8)))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12">
+        <f>AVERAGE(D7:D8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="13">
+        <f>AVERAGE(E7:E8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="13">
+        <f>AVERAGE(E7:E8)*(C12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="11">
-        <f>AVERAGE(D7:D8)</f>
-        <v>22892.385353496502</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="12">
-        <f>AVERAGE(E7:E8)</f>
-        <v>2.28923853534965</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="6">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="12">
-        <f>AVERAGE(E7:E8)*(C12)</f>
-        <v>7.0966394595839155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
+      <c r="D17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9">
+        <f>((C18)*(H18)*(I18))/(G18*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <f>D18/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="10">
+        <f>digestion_page!B21</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="10">
+        <f>digestion_page!C21</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <f>(LEFT(B18,FIND("/",B18)-1)/RIGHT(B18,LEN(B18)-FIND("/", B18)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9">
+        <f>((C19)*(H19)*(I19))/(G19*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <f>D19/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="10">
+        <f>digestion_page!B22</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="10">
+        <f>digestion_page!C22</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <f>(LEFT(B19,FIND("/",B19)-1)/RIGHT(B19,LEN(B19)-FIND("/", B19)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12">
+        <f>AVERAGE(D18:D19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="13">
+        <f>AVERAGE(E18:E19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="13">
+        <f>AVERAGE(E18:E19)*(C23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="B27" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:F18"/>
+  <mergeCells count="15">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F29"/>
   </mergeCells>
   <conditionalFormatting sqref="C14:F14">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(C14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:F25">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -900,76 +1101,417 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
+        <f>((C7)*(H7)*(I7))/(G7*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <f>D7/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <f>digestion_page!B12</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <f>digestion_page!C12</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <f>(LEFT(B7,FIND("/",B7)-1)/RIGHT(B7,LEN(B7)-FIND("/", B7)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
+        <f>((C8)*(H8)*(I8))/(G8*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <f>D8/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <f>digestion_page!B13</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <f>digestion_page!C13</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <f>(LEFT(B8,FIND("/",B8)-1)/RIGHT(B8,LEN(B8)-FIND("/", B8)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12">
+        <f>AVERAGE(D7:D8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="13">
+        <f>AVERAGE(E7:E8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="13">
+        <f>AVERAGE(E7:E8)*(C12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9">
+        <f>((C18)*(H18)*(I18))/(G18*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <f>D18/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="10">
+        <f>digestion_page!B23</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="10">
+        <f>digestion_page!C23</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <f>(LEFT(B18,FIND("/",B18)-1)/RIGHT(B18,LEN(B18)-FIND("/", B18)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5">
+        <f>"1/1"</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9">
+        <f>((C19)*(H19)*(I19))/(G19*1)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <f>D19/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="10">
+        <f>digestion_page!B24</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="10">
+        <f>digestion_page!C24</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <f>(LEFT(B19,FIND("/",B19)-1)/RIGHT(B19,LEN(B19)-FIND("/", B19)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12">
+        <f>AVERAGE(D18:D19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="13">
+        <f>AVERAGE(E18:E19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="13">
+        <f>AVERAGE(E18:E19)*(C23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="B27" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F29"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C14:F14">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(C14))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:F25">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(C25))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="16" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="16" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
